--- a/Config/GameConfig/Datas/__beans__.xlsx
+++ b/Config/GameConfig/Datas/__beans__.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Configs\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDC658C-4619-4B14-9187-E42535D1B838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E6762F-C574-4A62-94C3-9BD711B34042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,9 +110,6 @@
     <t>道具id</t>
   </si>
   <si>
-    <t>num</t>
-  </si>
-  <si>
     <t>道具数量</t>
   </si>
   <si>
@@ -211,6 +208,10 @@
   </si>
   <si>
     <t>item.ItemExchange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>count</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -218,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +258,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -287,7 +295,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -297,25 +305,39 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{958848DE-DA21-48BE-A795-CFA74084351B}"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="好 2" xfId="4" xr:uid="{4F3ACA50-5A21-48F1-A86D-BC7059F63D5C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -588,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
@@ -626,15 +648,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -692,11 +714,11 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>57</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="J4" t="s">
         <v>22</v>
@@ -709,166 +731,191 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J5" t="s">
-        <v>25</v>
+      <c r="J5" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" t="s">
         <v>31</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>32</v>
-      </c>
-      <c r="N7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" t="s">
         <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" t="s">
         <v>36</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>37</v>
-      </c>
-      <c r="N9" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" t="s">
         <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" t="s">
-        <v>40</v>
       </c>
       <c r="L10" t="s">
         <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" t="s">
         <v>32</v>
-      </c>
-      <c r="N11" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
         <v>44</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
         <v>45</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>46</v>
       </c>
-      <c r="G14" t="s">
+      <c r="J14" t="s">
         <v>47</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" t="s">
         <v>48</v>
-      </c>
-      <c r="L14" t="s">
-        <v>37</v>
-      </c>
-      <c r="N14" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>51</v>
       </c>
-      <c r="G15" t="s">
+      <c r="J15" t="s">
         <v>52</v>
       </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" t="s">
         <v>53</v>
-      </c>
-      <c r="L15" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" t="s">
+        <v>36</v>
+      </c>
+      <c r="N16" t="s">
         <v>55</v>
       </c>
-      <c r="L16" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" t="s">
-        <v>56</v>
-      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J21" s="2"/>
+      <c r="L21" s="4"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J22" s="2"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="5"/>
+      <c r="C24" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Config/GameConfig/Datas/__beans__.xlsx
+++ b/Config/GameConfig/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E6762F-C574-4A62-94C3-9BD711B34042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C48655-C433-4E42-97CD-A33A2DA4A71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -101,18 +101,9 @@
     <t>字段变体</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
-    <t>道具id</t>
-  </si>
-  <si>
-    <t>道具数量</t>
-  </si>
-  <si>
     <t>test.TestExcelBean1</t>
   </si>
   <si>
@@ -201,18 +192,6 @@
   </si>
   <si>
     <t>高度</t>
-  </si>
-  <si>
-    <t>,</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.ItemExchange</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>count</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -312,7 +291,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -322,14 +301,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -648,15 +624,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -714,182 +690,161 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" t="s">
-        <v>24</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="J5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" t="s">
-        <v>25</v>
-      </c>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
         <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
         <v>43</v>
       </c>
-      <c r="C14" t="s">
+      <c r="J14" t="s">
         <v>44</v>
       </c>
-      <c r="F14" t="s">
+      <c r="L14" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" t="s">
         <v>45</v>
-      </c>
-      <c r="G14" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" t="s">
-        <v>47</v>
-      </c>
-      <c r="L14" t="s">
-        <v>36</v>
-      </c>
-      <c r="N14" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="L15" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" t="s">
         <v>50</v>
-      </c>
-      <c r="G15" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" t="s">
-        <v>52</v>
-      </c>
-      <c r="L15" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
@@ -907,14 +862,14 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J21" s="2"/>
-      <c r="L21" s="4"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J22" s="2"/>
-      <c r="L22" s="4"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="5"/>
+      <c r="B24" s="3"/>
       <c r="C24" s="2"/>
     </row>
   </sheetData>
